--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260602141202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MULTISUMINISTROS DUMBOS, C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00003716</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOSBEIKER A. ROJAS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Falta un documento que no se pudo subir al primer momento</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_151936_0.png</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260602151936</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -482,11 +481,6 @@
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -552,11 +546,6 @@
           <t>INC_141202_0.png INC_141202_1.png</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ID_20260602141202</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,11 +609,6 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ID_20260602151936</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -412,8 +412,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="52.4609375" customWidth="1" min="12" max="13"/>
+    <col width="69.15234375" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -478,6 +482,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
@@ -541,7 +550,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>INC_141202_0.png INC_141202_1.png</t>
         </is>
@@ -606,7 +615,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
         </is>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,12 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="52.4609375" customWidth="1" min="12" max="13"/>
-    <col width="69.15234375" customWidth="1" min="14" max="14"/>
-  </cols>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -618,6 +615,76 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ROMA C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>000253911</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SKU duplicado SAL7556</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260604083947</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_083947_0.png INC_083947_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>INC_083947_0.png INC_083947_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FABRICA DE HIELO EL OSO, C.A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0000455</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Falta firma de Gerencia</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260604115119</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>INC_115119_0.png INC_115119_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,6 +755,76 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_115119_0.png INC_115119_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>026921</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Error en SKU duplicado RFR7512</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260605120143</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_120143_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -825,6 +825,77 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>INC_120143_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KC GLOBAL INT, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0000006610</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKU no pertenece a la recepcion
+</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260605140717</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>INC_140717_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,6 +896,76 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>INC_140717_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>001220</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Error en documentacion</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260605142914</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>INC_142914_0.png INC_142914_1.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,6 +966,71 @@
       <c r="N8" t="inlineStr">
         <is>
           <t>INC_142914_0.png INC_142914_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13869</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>YESIKA A. RUIZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Error en transcripcion al dorso</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260605153358</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1038,71 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>ID_20260605153358</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA CARIDAD C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>00471718</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Julio Canelon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No se indica diferencia al dorso del faltante en patas de pollo 200grs</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260606092604</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -1105,6 +1105,11 @@
           <t>ID_20260606092604</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>INC_092637_0.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +547,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_141202_0.png INC_141202_1.png</t>
@@ -619,6 +613,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
@@ -1040,76 +1035,7 @@
           <t>ID_20260605153358</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MORA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LA CARIDAD C.A.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>00471718</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Julio Canelon</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>TIPO A</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>No se indica diferencia al dorso del faltante en patas de pollo 200grs</t>
-        </is>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>SIN_FOTO</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>COBRO</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ID_20260606092604</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>INC_092637_0.png</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +554,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_141202_0.png INC_141202_1.png</t>
@@ -613,7 +619,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
@@ -1035,7 +1040,76 @@
           <t>ID_20260605153358</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA CARIDAD C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>00471718</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Julio Canelon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No se indica diferencia al dorso del faltante en patas de pollo 200grs</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260606092913</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>INC_092913_0.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_132921_0.jpeg</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,6 +1108,76 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>INC_092913_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7363</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JOHANA C. GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Falta firma y sello de sucursal</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260608090756</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>INC_090756_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,6 +547,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_141202_0.png INC_141202_1.png</t>
@@ -619,6 +613,7 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
@@ -1040,6 +1035,7 @@
           <t>ID_20260605153358</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1087,7 +1083,7 @@
           <t>No se indica diferencia al dorso del faltante en patas de pollo 200grs</t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" t="n">
         <v>0.25</v>
       </c>
       <c r="K10" t="inlineStr">

--- a/cuadros/JUNIO/MORA.xlsx
+++ b/cuadros/JUNIO/MORA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,7 +554,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_141202_0.png INC_141202_1.png</t>
@@ -613,7 +619,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_151936_0.png</t>
@@ -1035,7 +1040,6 @@
           <t>ID_20260605153358</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1083,7 +1087,7 @@
           <t>No se indica diferencia al dorso del faltante en patas de pollo 200grs</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="K10" t="inlineStr">
